--- a/Server/robos.xlsx
+++ b/Server/robos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Imágenes\Zonkray\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Imágenes\Zonkray\Server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4884F7-F01C-4A39-AF92-3EB6E6D6F126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046D85FD-2CF0-448D-A80D-5BA5A1037C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{002E2A53-079F-4612-B043-C484FB4741CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>Tipo de Robo</t>
   </si>
@@ -72,34 +72,6 @@
     <t>Robo a Banco central</t>
   </si>
   <si>
-    <t>Min = 1
-Max = 3</t>
-  </si>
-  <si>
-    <t>Min = 2
-Max = 4</t>
-  </si>
-  <si>
-    <t>Min = 4
-Max = 6</t>
-  </si>
-  <si>
-    <t>Min = 5
-Max = 6</t>
-  </si>
-  <si>
-    <t>Min = 3
-Max = 5</t>
-  </si>
-  <si>
-    <t>Min = 5
-Max = 7</t>
-  </si>
-  <si>
-    <t>Min = 6
-Max = 7</t>
-  </si>
-  <si>
     <t>Pistola</t>
   </si>
   <si>
@@ -135,8 +107,27 @@
 los delincuentes se podran retirar.</t>
   </si>
   <si>
-    <t>Si en 30 min no llega la poli
-los delincuentes se podran retirar.</t>
+    <t>Min = 5</t>
+  </si>
+  <si>
+    <t>Min = 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min = 2
+</t>
+  </si>
+  <si>
+    <t>Min = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min = 6
+</t>
+  </si>
+  <si>
+    <t>Min = 3</t>
+  </si>
+  <si>
+    <t>Min = 2</t>
   </si>
 </sst>
 </file>
@@ -575,16 +566,16 @@
         <v>5</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="8:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -596,19 +587,19 @@
     </row>
     <row r="15" spans="8:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="8:12" x14ac:dyDescent="0.25">
@@ -623,16 +614,16 @@
         <v>7</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="18" spans="8:12" x14ac:dyDescent="0.25">
@@ -647,16 +638,16 @@
         <v>6</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="20" spans="8:12" x14ac:dyDescent="0.25">
@@ -671,16 +662,16 @@
         <v>8</v>
       </c>
       <c r="I21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="K21" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="8:12" x14ac:dyDescent="0.25">
@@ -695,16 +686,16 @@
         <v>9</v>
       </c>
       <c r="I23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="K23" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="8:12" x14ac:dyDescent="0.25">
@@ -719,16 +710,16 @@
         <v>10</v>
       </c>
       <c r="I25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="K25" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Server/robos.xlsx
+++ b/Server/robos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Imágenes\Zonkray\Server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046D85FD-2CF0-448D-A80D-5BA5A1037C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E2E7EA-D7FF-45B3-ACC5-46FC30DC06CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{002E2A53-079F-4612-B043-C484FB4741CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
     <t>Tipo de Robo</t>
   </si>
@@ -128,6 +128,30 @@
   </si>
   <si>
     <t>Min = 2</t>
+  </si>
+  <si>
+    <t>Robo a Tren</t>
+  </si>
+  <si>
+    <t>Mini = 5</t>
+  </si>
+  <si>
+    <t>si en 20 min no llega la polí, podran retirarse del lugar</t>
+  </si>
+  <si>
+    <t>Robo a Yate</t>
+  </si>
+  <si>
+    <t>Mini = 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMG </t>
+  </si>
+  <si>
+    <t>Min = 6</t>
+  </si>
+  <si>
+    <t>Podran retirarse del lugar</t>
   </si>
 </sst>
 </file>
@@ -526,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{582BD4C7-238B-4707-9A1F-A95099C2A01D}">
-  <dimension ref="H11:L25"/>
+  <dimension ref="H11:L27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="7.7109375" customWidth="1"/>
@@ -534,7 +558,7 @@
     <col min="9" max="9" width="29" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="26" customWidth="1"/>
-    <col min="12" max="12" width="39.7109375" customWidth="1"/>
+    <col min="12" max="12" width="44.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
@@ -722,6 +746,40 @@
         <v>20</v>
       </c>
     </row>
+    <row r="26" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="8:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="H27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
